--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_05_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_05_21_Cau.xlsx
@@ -611,7 +611,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -625,7 +629,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là số cặp đã chạy đủ hai order.</t>
+          <t>Flip rate khi swap vị trí cặp câu trả lời A/B và B/A: (6 cặp đổi winner / 20 cặp đã thử) * 100% = 30%.</t>
         </is>
       </c>
     </row>
@@ -841,7 +845,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
@@ -855,7 +863,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số gồm toàn bộ case FAIL theo human gold.</t>
+          <t>True Positive Rate (TPR / Sensitivity / Recall) trên class FAIL: TP / (TP + FN) = 30 / (30 + 10) = 30 / 40 = 0,75 = 75%.</t>
         </is>
       </c>
     </row>
@@ -907,7 +915,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
@@ -921,7 +933,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính J rồi chia observed delta cho J.</t>
+          <t>Youden's J = TPR + TNR - 1 = 0,8 + 0,9 - 1 = 0,7. Công thức quan hệ observed delta ≈ J * true delta =&gt; true delta ≈ observed delta / J = 7 / 0,7 = 10 điểm phần trăm.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1413,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
@@ -1415,7 +1431,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ cộng hai ô hai version cho kết quả khác nhau.</t>
+          <t>Trong bảng 2x2 cho McNemar / exact-binomial test, số discordant pairs (cặp bất đồng) là tổng của hai ô chéo ngoài: b + c = 10 + 22 = 32.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_05_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_05_21_Cau.xlsx
@@ -660,10 +660,30 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Swap test cần policy cho từng outcome, không chỉ một tỷ lệ.
-Phân tích theo nguyên lý thiết kế: Swap test cần policy cho từng outcome, không chỉ một tỷ lệ.</t>
+- 1.0đ: Xử lý đúng nhóm Consistent Winners (70 ca) và Consistent Ties (20 ca) công nhận điểm số chính thức.
+- 1.0đ: Thiết lập quy tắc xử lý nghiêm ngặt cho 10 ca Flip Winners (không công nhận thắng, quy về Tie hoặc re-judge).
+- 1.0đ: Tính đúng tỷ lệ Position Inconsistency Rate = 10% trong báo cáo chẩn đoán.
+- 1.0đ: Thiết kế báo cáo bóc tách hướng thiên vị (First vs Second position bias / Primacy vs Recency effect).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cơ chế Xử lý Phán quyết (Verdict Handling) và Báo cáo Thiên vị Vị trí (Position Bias Report) cho 100 Cặp Thử nghiệm:
+1. **Quy tắc Xử lý Phán quyết Kỹ thuật (Verdict Handling Logic)**:
+- **Nhóm 1: Nhất quán Thắng thua (70 Consistent Winners)**:
+  + Xử lý: Công nhận kết quả chính thức không tranh cãi. Ứng viên nào thắng ở cả hai lượt `(A, B)` và `(B, A)` được cộng 1 điểm chiến thắng trọn vẹn.
+- **Nhóm 2: Nhất quán Hòa (20 Consistent Ties)**:
+  + Xử lý: Công nhận kết quả Hòa (Tie). Cả hai ứng viên nhận 0.5 điểm.
+- **Nhóm 3: Đảo ngược Kết quả do Thứ tự (10 Flip Winners - Bất nhất do Vị trí)**:
+  + Hiện tượng: Khi đưa `(A, B)` thì A thắng, nhưng khi tráo thành `(B, A)` thì B lại thắng (luôn ưu tiên người đứng đầu hoặc người đứng sau)!
+  + **Quy tắc Xử lý An toàn**: Tuyệt đối **KHÔNG CÔNG NHẬN CHIẾN THẮNG** cho bất kỳ bên nào trong 10 ca này. Áp dụng quy tắc phân xử: Đưa 10 ca này về trạng thái **HÒA DO THIÊN VỊ (Position-induced Tie)** hoặc chuyển tiếp sang một Giám khảo Phân xử độc lập bậc cao hơn (Tie-breaker Judge) để tái thẩm định.
+2. **Báo cáo Thiên vị Vị trí (Position Bias Diagnostic Report)**:
+- **Tỷ lệ Thiên vị Vị trí Tổng thể (Overall Position Inconsistency Rate)**:
+  $$\text{Position Flip Rate} = \frac{10}{100} \times 100\% = \mathbf{10.0\%}$$
+- **Báo cáo Hướng Thiên vị (Directional Positional Bias)**:
+  + Phân tích 10 ca bị lật: Xác định xem có bao nhiêu ca Judge luôn chọn lựa chọn ở **Vị trí 1 (First-position Bias)** so với lựa chọn ở **Vị trí 2 (Second-position Bias)**.   (Ví dụ: nếu 8/10 ca ưu ái người đứng đầu, kết luận Judge có khuynh hướng thiên vị thứ tự xuất hiện trước - Primacy Effect).
+- **Kiến nghị Vận hành**: Với tỷ lệ flip 10%, bắt buộc áp dụng cơ chế Position Swapping tự động cho 100% các bài đánh giá so sánh cặp trong tương lai.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiện tượng Thiên vị Vị trí trong LLM-as-a-Judge (Position Bias / Order Effect): Các mô hình ngôn ngữ lớn khi làm giám khảo so sánh cặp thường có xu hướng tâm lý thiên vị người được đọc trước (Primacy bias) hoặc người được đọc sau (Recency bias). Một quy trình thẩm định đạt chuẩn công nghiệp bắt buộc phải chạy hoán đổi thứ tự `(A,B)` và `(B,A)`. Những ca mà kết quả bị lật ngược theo vị trí (Flip winners) chứng minh khoảng cách chất lượng giữa hai bài thi là không đáng kể so với mức độ thiên vị của Judge, do đó phải được xử lý như một trận hòa hoặc đưa qua trọng tài phân xử.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Zheng et al.: Judging LLM-as-a-Judge with MT-Bench and Chatbot Arena (Section on Position Bias, NeurIPS 2023)</t>
         </is>
       </c>
     </row>
@@ -742,10 +762,27 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Probe chỉ có giá trị khi content target được kiểm soát.
-Phân tích theo nguyên lý thiết kế: Probe chỉ có giá trị khi content target được kiểm soát.</t>
+- 1.0đ: Thiết kế cặp thử nghiệm kiểm soát độ dài (Concise vs Verbose) giữ bất biến 100% dữ kiện thực tế.
+- 1.0đ: Thiết kế cặp thử nghiệm kiểm soát định dạng (Prose vs Bullet points) cùng nội dung.
+- 1.0đ: Thiết lập giải pháp prompt engineering răn đe chống thiên vị độ dài trong hợp đồng giám khảo.
+- 1.0đ: Đưa ra giải pháp hiệu chuẩn toán học chuẩn hóa độ dài (Length-normalized scoring regression).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Probe Thử nghiệm và Chiến lược Giảm thiểu Thiên vị Độ dài &amp; Định dạng (Verbosity &amp; Format Bias):
+1. **Thiết kế Cặp Thử nghiệm Đối chứng Nội dung Đồng nhất (Matched-Content Probes)**:
+- **Nguyên tắc**: Giữ nguyên vẹn 100% các dữ kiện sự thật, mệnh đề ngữ nghĩa và số liệu (Zero Semantic Difference); chỉ thao túng hình thức trình bày:
+- **Tạo 3 Biến thể Cặp Thử nghiệm**:
+  + **Cặp 1 (Độ dài - Length Probe)**: Cùng nội dung giải thích, Phiên bản $A_{\text{concise}}$ (súc tích, 80 từ) đối đầu Phiên bản $A_{\text{verbose}}$ (thêm 200 từ phụ giải thích lòng vòng, độn thêm từ đệm mà không có thông tin mới).
+  + **Cặp 2 (Định dạng - Format Probe)**: Cùng các bước hướng dẫn, Phiên bản $B_{\text{prose}}$ (viết thành đoạn văn liên tục) đối đầu Phiên bản $B_{\text{bullet}}$ (chia thành các gạch đầu dòng bullet points và in đậm từ khóa).
+  + **Đo lường Định lượng Mức độ Thiên vị (Bias Metric)**: Cho Judge chấm 100 cặp matched-content. Nếu tỷ lệ thiên vị câu trả lời dài hoặc bullet points $&gt; 70\%$, xác nhận Judge bị nhiễm thiên vị hình thức nghiêm trọng.
+2. **Chiến lược Giảm thiểu Toàn diện (Mitigation Strategies)**:
+- **Mitigation 1: Kỹ thuật Nhắc nhở Chống Thiên vị (Debiasing Prompt Contract)**:
+  Bổ sung chỉ thị răn đe rõ ràng trong System Prompt của Judge: 'CHÚ Ý: Đánh giá dựa trên chất lượng thông tin thực tế, TUYỆT ĐỐI KHÔNG ưu tiên câu trả lời dài hơn hay câu trả lời có gạch đầu dòng. Một câu trả lời ngắn gọn, trực diện nhưng đầy đủ ý phải được đánh giá cao hơn câu trả lời dài dòng vô ích.'
+- **Mitigation 2: Chuẩn hóa Độ dài theo Thống kê (Length-normalized Pairwise Scoring)**:
+  Áp dụng mô hình hồi quy logistic hiệu chỉnh độ dài: Điểm số so sánh được điều chỉnh bằng cách trừ đi hệ số hồi quy của độ chênh lệch số lượng từ: $\text{Score}_{\text{adjusted}} = \text{Score}_{\text{raw}} - \beta \times (\text{Length}_A - \text{Length}_B)$.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiện tượng Thiên vị Độ dài trong Đánh giá AI (Verbosity Bias): Các mô hình LLM có xu hướng vô thức đánh giá các câu trả lời dài dòng và định dạng bullet points bắt mắt là 'thông minh và hữu ích hơn', ngay cả khi nội dung hoàn toàn rỗng tuếch. Sử dụng các cặp thử nghiệm kiểm soát nội dung (Matched-content Probes) giúp vạch trần thiên vị này; và việc kết hợp giữa prompt chống thiên vị kèm hiệu chỉnh thống kê giúp đưa thước đo trở về đúng giá trị thực chất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Yann Dubois et al.: AlpacaEval: An Effective and Low-cost Evaluation of Instruction-following Language Models (Length-controlled AlpacaEval 2.0)</t>
         </is>
       </c>
     </row>
@@ -824,10 +861,27 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không quy mọi chênh lệch family thành quality.
-Phân tích theo nguyên lý thiết kế: Không quy mọi chênh lệch family thành quality.</t>
+- 1.0đ: Thiết kế thử nghiệm đối chứng mù giữa kết quả chấm của con người và hai dòng giám khảo khác nhau.
+- 1.0đ: Thiết lập công thức toán học ước lượng chỉ số thiên vị bản thân (Self-Affinity Index delta so với human gold).
+- 1.0đ: Thiết lập quy tắc thẩm định chéo bắt buộc (Cross-family judging) ngăn Judge chấm gà nhà.
+- 1.0đ: Xây dựng quy trình hội đồng đa dạng và cơ chế leo thang lên con người khi phát sinh xung đột quyền lợi mô hình.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Đo lường Độ Ái Kỷ Thiên vị Bản thân (Self-Preference Bias / Affinity Estimation) và Quy trình Leo thang:
+1. **Thiết kế Thử nghiệm Đo lường Mức độ Thiên vị (Affinity Estimation Framework)**:
+- Ba dòng mô hình tác giả (Author Families): $F_A$ (e.g., OpenAI GPT), $F_B$ (e.g., Anthropic Claude), $F_C$ (e.g., Meta Llama) cùng tạo câu trả lời trên 200 prompts chuẩn.
+- **Tập Chuẩn mực Đối chứng (Human Gold Baseline)**: Các chuyên gia con người chấm điểm mù (blind evaluation: xóa bỏ toàn bộ tên mô hình và metadata) để xác định tỷ lệ thắng khách quan thực tế.
+- **Chấm điểm bằng Hai Dòng Giám khảo Độc lập**: Đưa cùng tập bài thi cho Judge $J_A$ (thuộc dòng $F_A$) và Judge $J_B$ (thuộc dòng $F_B$) chấm độc lập.
+- **Công thức Ước lượng Hệ số Ái Kỷ (Self-Affinity Index)**:
+  $$\text{Affinity}(J_A, F_A) = \text{WinRate}_{J_A}(F_A) - \text{WinRate}_{\text{Human}}(F_A)$$
+  Nếu Judge $J_A$ chấm cho các câu trả lời của dòng họ $F_A$ thắng với tỷ lệ cao hơn 15 điểm phần trăm so với tỷ lệ do con người chấm ($+15\%$),   khẳng định Judge $J_A$ có thiên vị ái kỷ bản thân (Self-preference Bias) nghiêm trọng.
+2. **Quy trình Leo thang và Khử Thiên vị Vận hành (Escalation &amp; Mitigation Pipeline)**:
+- **Quy tắc Giám khảo Chéo Bắt buộc (Cross-Family Judging Gate)**: Tuyệt đối không cho phép một mô hình chấm điểm sản phẩm của chính dòng họ nó trong các cuộc so sánh cạnh tranh. Khi đánh giá mô hình thuộc $F_A$, bắt buộc phải sử dụng Judge thuộc $F_B$ hoặc $F_C$.
+- **Hội đồng Giám khảo Đa dạng (Multi-Family Panel Jury)**: Sử dụng một hội đồng gồm 3 Judge từ 3 họ khác nhau; kết quả là biểu quyết đa số hoặc trung bình có trọng số.
+- **Leo thang Chuyên gia Con người (Human Escalation Trigger)**: Bất cứ khi nào có sự bất đồng đối kháng sâu sắc (ví dụ $J_A$ chọn $F_A$ nhưng $J_B$ chọn $F_B$), vụ việc tự động được leo thang gửi tới Chuyên gia con người để phân xử chung cuộc.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiện tượng Tự Thiên vị trong LLM-as-a-Judge (Self-Enhancement / Egocentric Bias): Các nghiên cứu thực nghiệm (như MT-Bench, AlpacaEval) chỉ ra rằng các mô hình LLM có xu hướng ngầm ưu ái phong cách diễn đạt, cấu trúc câu và phân phối từ vựng của chính dòng họ mình (GPT thích GPT, Claude thích Claude). Bằng cách so sánh đối chiếu với kết quả chấm mù của con người, chúng ta định lượng được độ ái kỷ; và cơ chế thẩm định chéo (Cross-family jury) bảo đảm sự công bằng cho các kỳ thi đánh giá đa mô hình.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Zheng et al.: Judging LLM-as-a-Judge with MT-Bench (Self-Enhancement Bias Analysis, NeurIPS 2023) &amp; AlpacaEval Validation Studies</t>
         </is>
       </c>
     </row>
@@ -894,10 +948,38 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đặt từng ô theo human gold trước khi tính rate.
-Phân tích theo nguyên lý thiết kế: Đặt từng ô theo human gold trước khi tính rate.</t>
+- 1.0đ: Lập bảng ma trận nhầm lẫn chuẩn xác đầy đủ 4 ô: TP=12, FN=8, FP=8, TN=72.
+- 1.0đ: Tính đúng True Positive Rate (TPR) = 12 / 20 = 0.60 (60%).
+- 1.0đ: Tính đúng True Negative Rate (TNR) = 72 / 80 = 0.90 (90%).
+- 1.0đ: Đưa ra đề xuất leo thang chuyên gia con người xác đáng dựa trên tỷ lệ bỏ sót 40% lỗi của Judge.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lập Ma trận Nhầm lẫn (Confusion Matrix) với FAIL là Lớp Dương tính (Positive Class):
+- Quy ước bài toán: FAIL = Positive ($P$), PASS = Negative ($N$).
+  + Tổng số ca thực tế là FAIL (Actual Positives): $P = 20$ ca.
+  + Tổng số ca thực tế là PASS (Actual Negatives): $N = 80$ ca.
+- Dữ liệu quan sát:
+  + Judge đoán đúng FAIL: $\mathbf{TP = 12}$ (True Positive).
+  + Judge đoán đúng PASS: $\mathbf{TN = 72}$ (True Negative).
+- Tính toán các ô còn lại trong ma trận:
+  + Số ca thực tế là FAIL nhưng Judge đoán nhầm thành PASS: $\mathbf{FN} = P - \text{TP} = 20 - 12 = \mathbf{8}$ (Bỏ sót lỗi nguy hiểm).
+  + Số ca thực tế là PASS nhưng Judge đoán nhầm thành FAIL: $\mathbf{FP} = N - \text{TN} = 80 - 72 = \mathbf{8}$ (Báo động giả).
+| Thực tế (Ground Truth) \ Dự đoán (Judge) | Dự đoán FAIL (Predicted Positive) | Dự đoán PASS (Predicted Negative) | Tổng Thực tế |
+| :--- | :--- | :--- | :--- |
+| **Thực tế FAIL (Positive)** | **TP = 12** | **FN = 8** | 20 |
+| **Thực tế PASS (Negative)** | **FP = 8** | **TN = 72** | 80 |
+| **Tổng Dự đoán** | 20 | 80 | 100 |
+2. Tính toán TPR và TNR:
+- **True Positive Rate (TPR / Recall trên FAIL)**:
+  $$\text{TPR} = \frac{\text{TP}}{\text{TP} + \text{FN}} = \frac{12}{20} = \mathbf{0.60} \quad (60.0\%)$$
+- **True Negative Rate (TNR / Specificity trên PASS)**:
+  $$\text{TNR} = \frac{\text{TN}}{\text{TN} + \text{FP}} = \frac{72}{80} = \mathbf{0.90} \quad (90.0\%)$$
+3. Đề xuất Cơ chế Leo thang Giám sát (Escalation Proposal):
+- **Báo động Đỏ về Năng lực Phát hiện Lỗi**: TPR chỉ đạt 60% đồng nghĩa với việc Judge **đang bỏ lọt tới 40% số ca lỗi thực tế** ($8 / 20$ ca FAIL bị cho qua thành PASS).
+- **Quy tắc Leo thang Tự động**: Bổ sung tầng kiểm tra độ tự tin (Confidence Scoring). Bất kỳ ca nào mà Judge gán nhãn PASS nhưng điểm tự tin $&lt; 0.85$ hoặc nằm trong các danh mục rủi ro cao (an toàn, bảo mật, tài chính) bắt buộc phải được **Leo thang tự động gửi tới Chuyên gia Con người (Human Escalation)** để tái kiểm tra, ngăn chặn lỗi lọt lưới.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đánh giá Giám khảo với Lớp Dương tính là Lỗi (Treating Failures as the Positive Class): Trong kiểm thử chất lượng, mục tiêu tối thượng là bắt lỗi. Nếu coi PASS là positive, chỉ số Accuracy 84% tạo ra cảm giác an tâm giả tạo. Khi đảo góc nhìn chuẩn mực: coi FAIL là Positive, chúng ta nhìn thấy ngay sự thật tồi tệ: Judge bỏ sót 40% lỗi vi phạm (Recall chỉ đạt 60%). Cơ chế leo thang con người là lớp lưới an toàn bắt buộc để bù đắp cho điểm mù này của Judge.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Tom Fawcett: An Introduction to ROC Analysis (Pattern Recognition Letters, 2006) &amp; Medical Diagnostic Testing Standards</t>
         </is>
       </c>
     </row>
@@ -964,10 +1046,23 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Công thức không cứu được comparison confounded.
-Phân tích theo nguyên lý thiết kế: Công thức không cứu được comparison confounded.</t>
+- 1.0đ: Đưa ra phán quyết dứt khoát: CẤM hiệu chỉnh delta thành 8%.
+- 1.0đ: Chỉ ra lỗ hổng phương pháp luận cốt tử: prompt của Judge bị đổi làm mất tính bất biến của thước đo.
+- 1.0đ: Phân tích vì sao không thể áp dụng phép chia tuyến tính $4\% / 0.5$ trên các mô hình xác suất LLM.
+- 1.0đ: Đưa ra quy trình khắc phục chuẩn mực (đóng băng một phiên bản judge duy nhất hoặc dùng human gold).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phán quyết Kỹ thuật (Technical Verdict): **TUYỆT ĐỐI KHÔNG ĐƯỢC PHÉP HIỆU CHỈNH DELTA THÀNH 8 ĐIỂM PHẦN TRĂM (DO NOT ADJUST DELTA TO 8%)**.
+2. Lập luận Phân tích Sai phạm Phương pháp luận (Methodological Flaw Analysis):
+- **Nhiễu Loạn Biến số Cực độ (Extreme Variable Confounding)**: Ý tưởng 'hiệu chỉnh' lấy độ chênh lệch thô $16\% - 12\% = 4\%$ rồi chia cho hệ số tin cậy $J = 0.5$ để ra $4\% / 0.5 = 8\%$ dựa trên giả định ngây thơ rằng Judge hoạt động như một cảm biến tuyến tính không đổi. Tuy nhiên, đề bài nêu rõ: **Prompt của Judge CŨNG ĐÃ BỊ THAY ĐỔI ở phiên bản V2**!
+- **Mất Chuẩn Thước Đo (Loss of Measurement Invariance)**: Khi prompt của Judge bị sửa đổi, bản thân cái 'thước đo' đã bị thay đổi độ khắt khe, tiêu chuẩn và thang điểm. Mức tăng từ 12% lên 16% hoàn toàn có thể chỉ là do Judge mới có prompt gắt gao hơn, bắt nhiều lỗi vụn vặt hơn, chứ không hề chứng minh được ứng dụng V2 bị tăng tỷ lệ lỗi thực tế.
+- **Công thức Tuyến tính Không Hợp lệ**: Trong thống kê phi tham số và mô hình ngôn ngữ xác suất, sai số của Judge không phân bổ đồng nhất và không thể nhân chia tỷ lệ một cách thô thiển.
+3. Hành động Khắc phục Chuẩn mực để Tìm Delta Thật (Legitimate Verification Action):
+- Khóa cứng (Freeze) một phiên bản Judge duy nhất (ví dụ dùng lại Judge Prompt của V1).
+- Chạy lại cả ứng dụng V1 và V2 dưới cùng một Judge Prompt bất biến này để đo lường $\Delta$ thực sự; hoặc tốt nhất là lấy mẫu 100 ca có bất đồng đưa cho Chuyên gia con người chấm mù (Blind Human Annotation) để xác lập delta chân lý.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Bất biến của Thiết bị Đo lường (Measurement Invariance Principle): Trong bất kỳ thí nghiệm khoa học nào, bạn không thể vừa thay đổi đối tượng thử nghiệm (V1 -&gt; V2) vừa thay đổi dụng cụ đo (Judge Prompt V1 -&gt; Judge Prompt V2) rồi dùng toán học nhân chia cơ học để suy diễn kết quả. Hành vi tự ý nhân đôi delta từ 4% lên 8% là ngụy tạo thống kê (statistical fabrication) và vi phạm nghiêm trọng tính liêm chính trong kiểm thử.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+David Hand: Measurement Theory and Practice &amp; Andrew Gelman: Data Analysis Using Regression and Multilevel/Hierarchical Models</t>
         </is>
       </c>
     </row>
@@ -1046,10 +1141,26 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Majority count cần được đọc cùng error dependence.
-Phân tích theo nguyên lý thiết kế: Majority count cần được đọc cùng error dependence.</t>
+- 1.0đ: Vạch trần nguy cơ của liên minh đa số giả tạo khi dùng biểu quyết giản đơn với giám khảo bị tương quan.
+- 1.0đ: Thiết kế cơ chế tổng hợp phân bổ trọng số hợp lý (chia đôi trọng số của cụm Judge 1 &amp; 3, nâng vị thế Judge 2).
+- 1.0đ: Xác định chính xác các điều kiện kích hoạt leo thang con người (High-risk tie và bất đồng giữa hai nhánh độc lập).
+- 1.0đ: Mô tả quy trình đưa ca bất đồng vào hàng đợi thẩm định của chuyên gia con người (Human review queue).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cơ chế Tổng hợp Hội đồng Giám khảo (Aggregation) và Quy trình Leo thang (Escalation) khi có Giám khảo Tương quan:
+1. **Bản chất của Lỗi Tương quan (Correlated Judge Trap / Multi-collinearity)**:
+Panel gồm 3 Judge nhưng Judge 3 gần như 'copy lỗi' của Judge 1 (tương quan lỗi cực cao, $\rho \approx 1.0$). Nếu áp dụng cơ chế bỏ phiếu đa số giản đơn (Simple Majority Voting 2/3), Judge 1 và Judge 3 sẽ tạo thành một 'liên minh đa số giả tạo' (Correlated False Majority) đè bẹp phán quyết độc lập của Judge 2, làm vô hiệu hóa hoàn toàn lợi ích của hội đồng đa giám khảo.
+2. **Thiết kế Cơ chế Tổng hợp Khử Tương quan (Decorrelated Aggregation Contract)**:
+- **Hạ trọng số Giám khảo Phụ thuộc (Down-weighting Correlated Judge)**: Áp dụng cơ chế gán trọng số dựa trên tính độc lập thông tin: Judge 2 (độc lập) nhận trọng số $W_2 = 0.50$; cụm tương quan (Judge 1 và Judge 3) chia đôi trọng số còn lại: $W_1 = 0.25$ và $W_3 = 0.25$.
+- **Điểm số Tổng hợp có Trọng số**: $$\text{Consensus Score} = 0.25 \times S_1 + 0.50 \times S_2 + 0.25 \times S_3$$
+3. **Quy trình Leo thang Rà soát Con người (Human Escalation Protocol)**:
+- **Điều kiện kích hoạt Leo thang Khẩn cấp (Escalation Triggers)**:
+  + **Điều kiện 1 (High-risk Tie)**: Khi điểm tổng hợp rơi vào vùng lưỡng lự $0.45 \le \text{Consensus Score} \le 0.55$ trong các tác vụ có mức độ rủi ro cao (High-risk domain: y tế, tài chính, an toàn).
+  + **Điều kiện 2 (Bất đồng giữa hai nguồn độc lập)**: Khi Judge 1 và Judge 2 đưa ra phán quyết hoàn toàn trái ngược nhau (Judge 1 gán PASS, Judge 2 gán FAIL).
+- **Hành động Leo thang**: Đóng băng kết quả tự động; trích xuất toàn bộ context và gửi case về hàng đợi review của Chuyên gia con người (Human-in-the-loop Queue) để phân xử chung cuộc.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Hội đồng Độc lập trong Đánh giá AI (Ensemble Diversity &amp; Decorrelation): Giá trị của một hội đồng giám khảo (Judge Panel) chỉ tồn tại khi các giám khảo mắc lỗi độc lập với nhau (Independent Error Distributions - Condorcet's Jury Theorem). Nếu đưa vào 2 giám khảo dùng cùng một base model hoặc cùng một prompt, họ sẽ cùng mắc chung một điểm mù. Hạ trọng số các giám khảo trùng lặp và kích hoạt chốt chặn con người khi có bất đồng giữa các nguồn độc lập là thiết kế chuẩn mực.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Condorcet's Jury Theorem &amp; Ensemble Methods in Machine Learning (Dietterich, 2000) &amp; Anthropic Multi-evaluator Protocols</t>
         </is>
       </c>
     </row>
@@ -1176,10 +1287,25 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: CI phải được diễn giải trong design đã chạy.
-Phân tích theo nguyên lý thiết kế: CI phải được diễn giải trong design đã chạy.</t>
+- 1.0đ: Bác bỏ tuyên bố 'B tốt hơn A' dựa trên hiện tượng chồng lấn sâu của hai khoảng tin cậy ([74%, 84%]).
+- 1.0đ: Giải thích rõ ràng nguyên nhân do kích thước mẫu nhỏ làm sai số chuẩn lớn, chưa đạt ý nghĩa thống kê.
+- 1.0đ: Đề xuất phương pháp kiểm định chênh lệch cặp chuẩn xác (Paired difference bootstrap / McNemar test).
+- 1.0đ: Đưa ra hành động kỹ thuật mở rộng cỡ mẫu dựa trên phân tích năng lực thống kê (Power Analysis).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Diễn giải Bằng chứng Thống kê Thực tế (Interpretation of Statistical Evidence):
+- Dữ liệu quan sát: Phiên bản A đạt Pass Rate 78% với Khoảng tin cậy 95% (CI): $[70\%, 84\%]$. Phiên bản B đạt 82% với CI: $[74\%, 88\%]$.
+- **Bằng chứng CHƯA ĐỦ để Khẳng định B Tốt hơn A (Insufficient Evidence to Claim B &gt; A)**:
+  + Hai khoảng tin cậy độc lập bị **chồng lấn rất lớn** (khoảng giao thoa từ 74% đến 84%).
+  + Mặc dù điểm ước lượng điểm (Point Estimate) của B cao hơn A là $+4\%$, nhưng do kích thước mẫu quá nhỏ (Small Paired Suite), sai số chuẩn (Standard Error) còn rất lớn.   Sự khác biệt 4 điểm hoàn toàn có thể chỉ là do biến động ngẫu nhiên của mẫu (Random Chance / Sampling Noise) chứ không có ý nghĩa thống kê ở mức $\alpha = 0.05$.
+2. Đề xuất Bước Kế tiếp Chuẩn mực Kỹ thuật (Actionable Next Steps):
+- **Bước 1: Tính toán Khoảng Tin cậy cho Chênh lệch Cặp (Paired Difference CI)**:
+  Vì bài kiểm tra là Paired Suite (A và B chạy trên cùng tập prompt), không được so sánh hai CI độc lập!   Bắt buộc phải tính toán khoảng tin cậy của chênh lệch trực tiếp $\Delta = B_i - A_i$ (bằng kỹ thuật Paired Bootstrap hoặc McNemar test).   Nếu khoảng tin cậy của $\Delta$ chứa giá trị $0$ (ví dụ $\text{CI}_{\Delta} = [-2\%, +10\%]$), khẳng định 100% chưa có ý nghĩa thống kê.
+- **Bước 2: Mở rộng Kích thước Mẫu Kiểm thử (Sample Size Expansion)**:
+  Tiến hành phân tích Năng lực Thống kê (Power Analysis) để tính toán số lượng ca test cần thiết (thường cần từ 300-500 ca)   để thu hẹp độ rộng khoảng tin cậy xuống $\pm 2\%$, bảo đảm phát hiện được mức tăng 4 điểm một cách chắc chắn trước khi công bố B tốt hơn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Sử dụng Khoảng Tin cậy trong Kiểm thử Phần mềm AI (Confidence Intervals vs Overclaiming): Trong kiểm thử AI, việc nhìn vào điểm số trung bình (82% &gt; 78%) để vội vàng tuyên bố chiến thắng là lỗi 'Confirmation Bias' điển hình. Khoảng tin cậy rộng phản ánh sự bất định cao do kích thước mẫu nhỏ. Một kỹ sư chuyên nghiệp phải phân tích sự chồng lấn của khoảng tin cậy, thực hiện kiểm định chênh lệch cặp (paired analysis) và kiên quyết bác bỏ các tuyên bố cải tiến chưa đạt ý nghĩa thống kê.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+David L. Streiner: Maintaining Sanity at Confidence Intervals &amp; Kohavi, Tang, Xu: Trustworthy Online Controlled Experiments (Cambridge University Press)</t>
         </is>
       </c>
     </row>
@@ -1306,10 +1432,29 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không có một case count phổ quát.
-Phân tích theo nguyên lý thiết kế: Không có một case count phổ quát.</t>
+- 1.0đ: Liệt kê đầy đủ 5 tham số đầu vào bắt buộc (baseline p1, MDE delta, alpha, power, test design).
+- 1.0đ: Phân tích và chỉ rõ hiện trạng 25 ca là thiếu năng lực thống kê nghiêm trọng (severely underpowered).
+- 1.0đ: Trình bày công thức/ước lượng số học chứng minh cỡ mẫu thực tế cần tới hàng trăm/nghìn ca để phát hiện delta 5%.
+- 1.0đ: Đưa ra hành động kỹ thuật thực tế (mở rộng mẫu hoặc chuyển sang rà soát chuyên gia định tính).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Các Tham số Đầu vào Bắt buộc cho Bài toán Xác định Cỡ mẫu (Sample Size Calculation Inputs):
+Để tính toán cỡ mẫu cần thiết ($N$) theo lý thuyết thống kê kiểm định giả thuyết hai tỷ lệ, nhóm kỹ sư bắt buộc phải có đủ 5 tham số:
+- **Tỷ lệ đường cơ sở (Baseline Rate - $p_1$)**: $p_1 = 0.70$ (70% theo đề bài).
+- **Mức độ tác động tối thiểu cần phát hiện (Minimum Detectable Effect - $\delta$ / MDE)**: $\delta = +0.05$ (5 điểm phần trăm), tức $p_2 = p_1 + \delta = 0.75$.
+- **Mức ý nghĩa thống kê (Significance Level - $\alpha$)**: Thường chọn chuẩn $\alpha = 0.05$ (mức tin cậy 95%, kiểm định hai phía $Z_{\alpha/2} = 1.96$).
+- **Năng lực thống kê mong muốn (Statistical Power - $1 - \beta$)**: $1 - \beta = 0.80$ ($80\%$, tương ứng xác suất phạm sai lầm loại II là $\beta = 0.20$, $Z_\beta = 0.84$).
+- **Thiết kế Thử nghiệm (Test Design Type)**: Kiểm định mẫu độc lập (Two-sample proportion test) hay Kiểm định cặp đối chứng (Paired discordant test).
+2. Phân tích Hiện trạng Mẫu 25 Ca và Hành động Kỹ thuật Cụ thể:
+- **Đánh giá Hiện trạng 25 ca**: **HOÀN TOÀN BẤT LỰC (SEVERELY UNDERPOWERED)**.   Theo công thức cỡ mẫu chuẩn cho kiểm định tỷ lệ hai phía:
+  $$N \approx \frac{(Z_{\alpha/2} + Z_\beta)^2 \times [p_1(1-p_1) + p_2(1-p_2)]}{(p_2 - p_1)^2} = \frac{(1.96 + 0.84)^2 \times [0.70(0.30) + 0.75(0.25)]}{(0.05)^2} \approx \frac{7.84 \times [0.210 + 0.1875]}{0.0025} \approx \mathbf{1.246 \text{ ca/nhóm}}$$
+  Với chỉ vỏn vẹn **25 ca**, năng lực thống kê thực tế $&lt; 10\%$, nghĩa là việc đo lường mức tăng 5% chỉ là trò chơi may rủi tung đồng xu.
+- **Hành động Kỹ thuật Bắt buộc (Action Items)**:
+  + **Hành động 1 (Mở rộng Mẫu)**: Thu thập thêm dữ liệu thực tế hoặc sinh dữ liệu tổng hợp (synthetic cases) có thẩm định để mở rộng lát cắt critical slice lên quy mô tối thiểu vài trăm ca.
+  + **Hành động 2 (Tái định vị Mục tiêu)**: Nếu không thể có quá 25 ca (do ca bệnh cực hiếm), phải chấp nhận thực tế: từ bỏ mục tiêu phát hiện delta nhỏ 5%, chuyển sang kiểm thử định tính chuyên gia con người (Qualitative Expert Review 100%) hoặc chỉ phát hiện các mức sụt giảm thảm họa cực lớn ($\Delta &gt; 30\%$).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Năng lực Thống kê và Cỡ Mẫu (Statistical Power Analysis): Đo lường một hiệu ứng nhỏ (5 điểm phần trăm) đòi hỏi một cỡ mẫu rất lớn (hơn một nghìn ca) để triệt tiêu nhiễu nhị phân. Việc đem 25 ca test ra để cố gắng chứng minh một mô hình 'tốt hơn 5%' là ngộ nhận toán học nghiêm trọng. Hiểu rõ công thức tính cỡ mẫu giúp kỹ sư không lãng phí thời gian vào các thử nghiệm vô nghĩa và biết khi nào cần chuyển sang đánh giá định tính chuyên sâu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jacob Cohen: Statistical Power Analysis for the Behavioral Sciences &amp; Fleiss, Levin, Paik: Statistical Methods for Rates and Proportions</t>
         </is>
       </c>
     </row>
@@ -1392,10 +1537,27 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nondeterminism control phải đối xứng.
-Phân tích theo nguyên lý thiết kế: Nondeterminism control phải đối xứng.</t>
+- 1.0đ: Chỉ ra lỗ hổng phương pháp luận nghiêm trọng: so sánh lệch ngân sách tính toán (Single-run vs Best-of-3).
+- 1.0đ: Phân tích hiện tượng đánh tráo giữa năng lực prompt với hiệu ứng lấy mẫu nhiều lần (sampling/reranking effect).
+- 1.0đ: Thiết kế Phương án sửa A: chuẩn hóa cả hai về chế độ Single-run với temperature=0 có kiểm soát.
+- 1.0đ: Thiết kế Phương án sửa B: chuẩn hóa cả hai cùng chạy Best-of-3 ngang hàng về tài nguyên tính toán.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lỗ hổng Phương pháp luận Cốt tử trong Giao thức Hiện tại (Protocol Flaw Analysis):
+- **So sánh Bất công / Lệch Ngân sách Tính toán (Unfair Compute Budget Asymmetry)**: Phiên bản V1 chỉ được chạy duy nhất 1 lần (Single-run), trong khi V2 được chạy 3 lần và chọn kết quả tốt nhất (Best-of-3).
+- **Đánh tráo Năng lực Mô hình với Kỹ thuật Tìm kiếm (Confounding Capability with Search/Reranking)**: Nếu V2 đạt điểm cao hơn, nhóm kỹ sư không thể biết được mức tăng đó là do prompt của V2 tốt hơn, hay thuần túy là do V2 được hưởng lợi từ việc lấy mẫu 3 lần và thuật toán reranking (pass@3 / best-of-k effect). Đây là một cuộc thử nghiệm thiên vị có chủ đích, vi phạm nguyên tắc kiểm soát biến số khoa học.
+2. Sửa đổi Giao thức Kiểm thử để So sánh Hợp lệ (Revised Controlled Protocols):
+- Để cuộc so sánh có giá trị khoa học và được chấp nhận cho cổng release, nhóm bắt buộc phải chọn **MỘT TRONG HAI GIAO THỨC CHUẨN** sau:
+- **Phương án A: Giao thức Đối chứng Đơn lượt Ngang hàng (Controlled Single-Run Protocol - Khuyến nghị cho CI)**:
+  + Cả V1 và V2 cùng chạy **đúng 1 lần duy nhất** trên cùng 100 ca test.
+  + Khóa cố định các siêu tham số: `temperature = 0` (hoặc cùng chung seed nếu $T &gt; 0$).
+  + Đảm bảo đo lường năng lực suy luận nội tại thuần túy của Prompt mới mà không bị nhiễu bởi cơ chế retry.
+- **Phương án B: Giao thức Đối chứng Cùng Ngân sách Tìm kiếm (Controlled Best-of-3 Protocol)**:
+  + Nếu sản phẩm thực tế trên production cho phép chạy Best-of-3, thì **CẢ V1 VÀ V2 ĐỀU PHẢI CHẠY BEST-OF-3** với cùng chung một thuật toán chấm điểm reranker.
+  + So sánh công bằng hiệu quả của hai phiên bản khi cùng được cấp phát một ngân sách tính toán (compute budget) tương đương nhau.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Cân bằng Ngân sách Tính toán trong Thử nghiệm AI (Controlled Evaluation &amp; Compute Parity): Kỹ thuật Best-of-k (sinh $k$ câu trả lời và chọn câu tốt nhất) luôn luôn tạo ra bước nhảy vọt về chất lượng so với sinh 1 câu đơn lẻ. Đem một giải pháp Best-of-3 so sánh với một giải pháp Single-run rồi kết luận 'Prompt mới thông minh hơn' là sự ngụy biện. Một giao thức hợp lệ bắt buộc phải bảo đảm tính đối xứng tuyệt đối về số lần chạy và tài nguyên tính toán giữa hai phiên bản.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Best-of-N Evaluation Standards &amp; Stanford HELM: Standardizing Evaluation Environments</t>
         </is>
       </c>
     </row>
